--- a/plate3d/PLATE3D_BASIC.xlsx
+++ b/plate3d/PLATE3D_BASIC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="146">
   <si>
     <t>BASIC example - every keyword, one small model</t>
   </si>
@@ -190,6 +190,51 @@
     <t>C</t>
   </si>
   <si>
+    <t>bracket: shallow tip …</t>
+  </si>
+  <si>
+    <t>sc.brkt</t>
+  </si>
+  <si>
+    <t>tc</t>
+  </si>
+  <si>
+    <t>… deepening to the column</t>
+  </si>
+  <si>
+    <t>sc.brk</t>
+  </si>
+  <si>
+    <t># TAPER</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>start.pt</t>
+  </si>
+  <si>
+    <t>end.pt</t>
+  </si>
+  <si>
+    <t>taper.pt</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>tc tc keeps the top flange flat</t>
+  </si>
+  <si>
+    <t>TAPER</t>
+  </si>
+  <si>
+    <t>tp.brk</t>
+  </si>
+  <si>
     <t># CUT</t>
   </si>
   <si>
@@ -260,6 +305,9 @@
   </si>
   <si>
     <t>YZ</t>
+  </si>
+  <si>
+    <t>YZ grows +X: tip at -610, stopping at the cleat face</t>
   </si>
   <si>
     <t>LX1</t>
@@ -794,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1015,7 +1063,6 @@
         <v>320</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
@@ -1102,7 +1149,6 @@
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
@@ -1143,7 +1189,6 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>11</v>
@@ -1358,190 +1403,210 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22">
+        <v>500</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22">
+        <v>110</v>
+      </c>
+      <c r="I22">
+        <v>150</v>
+      </c>
+      <c r="J22">
+        <v>150</v>
+      </c>
+      <c r="K22">
+        <v>8</v>
+      </c>
+      <c r="L22">
+        <v>12</v>
+      </c>
+      <c r="M22">
+        <v>12</v>
+      </c>
+      <c r="N22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23">
+        <v>500</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23">
+        <v>200</v>
+      </c>
+      <c r="I23">
+        <v>150</v>
+      </c>
+      <c r="J23">
+        <v>150</v>
+      </c>
+      <c r="K23">
+        <v>8</v>
+      </c>
+      <c r="L23">
+        <v>12</v>
+      </c>
+      <c r="M23">
+        <v>12</v>
+      </c>
+      <c r="N23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
         <v>60</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E26" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" t="s">
         <v>61</v>
       </c>
-      <c r="E23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23" t="s">
-        <v>64</v>
-      </c>
-      <c r="I23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24">
-        <v>-150</v>
-      </c>
-      <c r="E24">
-        <v>-150</v>
-      </c>
-      <c r="F24" t="s">
-        <v>29</v>
-      </c>
-      <c r="G24">
-        <v>300</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25">
-        <v>-150</v>
-      </c>
-      <c r="E25">
-        <v>150</v>
-      </c>
-      <c r="F25" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25">
-        <v>300</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26">
-        <v>-130</v>
-      </c>
-      <c r="E26">
-        <v>-130</v>
-      </c>
-      <c r="F26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27">
-        <v>-50</v>
-      </c>
-      <c r="E27">
-        <v>-50</v>
-      </c>
-      <c r="F27" t="s">
-        <v>29</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>50</v>
-      </c>
-      <c r="I27">
-        <v>2</v>
+      <c r="G26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26">
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>66</v>
+      <c r="B28" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28">
-        <v>50</v>
-      </c>
-      <c r="E28">
-        <v>-50</v>
+        <v>75</v>
+      </c>
+      <c r="D28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" t="s">
+        <v>77</v>
       </c>
       <c r="F28" t="s">
+        <v>5</v>
+      </c>
+      <c r="G28" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" t="s">
+        <v>79</v>
+      </c>
+      <c r="I28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29">
+        <v>-150</v>
+      </c>
+      <c r="E29">
+        <v>-150</v>
+      </c>
+      <c r="F29" t="s">
         <v>29</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>50</v>
-      </c>
-      <c r="I28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="s">
-        <v>31</v>
+      <c r="G29">
+        <v>300</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1549,22 +1614,22 @@
         <v>11</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D30">
-        <v>-170</v>
+        <v>-150</v>
       </c>
       <c r="E30">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="F30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G30">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1573,53 +1638,53 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D31">
-        <v>-170</v>
+        <v>-130</v>
       </c>
       <c r="E31">
-        <v>150</v>
+        <v>-130</v>
       </c>
       <c r="F31" t="s">
-        <v>30</v>
-      </c>
-      <c r="G31">
-        <v>340</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>50</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1627,125 +1692,126 @@
         <v>11</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D33">
-        <v>-88</v>
+        <v>50</v>
       </c>
       <c r="E33">
-        <v>-88</v>
+        <v>-50</v>
       </c>
       <c r="F33" t="s">
         <v>29</v>
       </c>
       <c r="G33">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35">
+        <v>-170</v>
+      </c>
+      <c r="E35">
+        <v>-150</v>
+      </c>
+      <c r="F35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35">
+        <v>340</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36">
+        <v>-170</v>
+      </c>
+      <c r="E36">
+        <v>150</v>
+      </c>
+      <c r="F36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36">
+        <v>340</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s">
         <v>25</v>
       </c>
-      <c r="D34">
-        <v>-88</v>
-      </c>
-      <c r="E34">
-        <v>88</v>
-      </c>
-      <c r="F34" t="s">
-        <v>29</v>
-      </c>
-      <c r="G34">
-        <v>176</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" t="s">
-        <v>61</v>
-      </c>
-      <c r="G36" t="s">
-        <v>62</v>
-      </c>
-      <c r="H36" t="s">
-        <v>71</v>
-      </c>
-      <c r="I36" t="s">
-        <v>72</v>
-      </c>
-      <c r="J36" t="s">
-        <v>73</v>
-      </c>
-      <c r="K36" t="s">
-        <v>74</v>
-      </c>
-      <c r="L36" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37" t="s">
-        <v>80</v>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1753,28 +1819,28 @@
         <v>11</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="D38">
+        <v>-88</v>
+      </c>
+      <c r="E38">
+        <v>-88</v>
+      </c>
+      <c r="F38" t="s">
+        <v>29</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="H38">
-        <v>25</v>
-      </c>
-      <c r="I38" t="s">
-        <v>80</v>
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -1782,365 +1848,416 @@
         <v>11</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" t="s">
-        <v>79</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="D39">
+        <v>-88</v>
+      </c>
+      <c r="E39">
+        <v>88</v>
+      </c>
+      <c r="F39" t="s">
+        <v>29</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="H39">
-        <v>3025</v>
-      </c>
-      <c r="I39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" t="s">
-        <v>78</v>
-      </c>
-      <c r="D40" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" t="s">
-        <v>81</v>
-      </c>
-      <c r="F40">
-        <v>-100</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>2600</v>
-      </c>
-      <c r="I40" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E41" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G41" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L41" t="s">
-        <v>89</v>
-      </c>
-      <c r="M41" t="s">
         <v>90</v>
       </c>
-      <c r="N41" t="s">
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B42" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>94</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42">
-        <v>-150</v>
-      </c>
-      <c r="G42">
-        <v>-150</v>
-      </c>
-      <c r="H42">
-        <v>25</v>
-      </c>
-      <c r="I42">
-        <v>-150</v>
-      </c>
-      <c r="J42">
-        <v>-150</v>
-      </c>
-      <c r="K42">
-        <v>-250</v>
-      </c>
-      <c r="L42">
-        <v>-50</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D43" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="E43" t="s">
         <v>11</v>
       </c>
       <c r="F43">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>25</v>
       </c>
-      <c r="I43">
-        <v>150</v>
-      </c>
-      <c r="J43">
+      <c r="I43" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>3025</v>
+      </c>
+      <c r="I44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F45">
+        <v>-100</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>2600</v>
+      </c>
+      <c r="I45" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" t="s">
+        <v>73</v>
+      </c>
+      <c r="F46">
+        <v>-610</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>2600</v>
+      </c>
+      <c r="I46" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" t="s">
+        <v>85</v>
+      </c>
+      <c r="F47" t="s">
+        <v>99</v>
+      </c>
+      <c r="G47" t="s">
+        <v>100</v>
+      </c>
+      <c r="H47" t="s">
+        <v>101</v>
+      </c>
+      <c r="I47" t="s">
+        <v>102</v>
+      </c>
+      <c r="J47" t="s">
+        <v>103</v>
+      </c>
+      <c r="K47" t="s">
+        <v>104</v>
+      </c>
+      <c r="L47" t="s">
+        <v>105</v>
+      </c>
+      <c r="M47" t="s">
+        <v>106</v>
+      </c>
+      <c r="N47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48" t="s">
+        <v>108</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48">
         <v>-150</v>
       </c>
-      <c r="K43">
-        <v>-250</v>
-      </c>
-      <c r="L43">
-        <v>-50</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" t="s">
-        <v>78</v>
-      </c>
-      <c r="D44" t="s">
-        <v>94</v>
-      </c>
-      <c r="E44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44">
+      <c r="G48">
         <v>-150</v>
-      </c>
-      <c r="G44">
-        <v>150</v>
-      </c>
-      <c r="H44">
-        <v>25</v>
-      </c>
-      <c r="I44">
-        <v>-150</v>
-      </c>
-      <c r="J44">
-        <v>150</v>
-      </c>
-      <c r="K44">
-        <v>-250</v>
-      </c>
-      <c r="L44">
-        <v>-50</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" t="s">
-        <v>78</v>
-      </c>
-      <c r="D45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45">
-        <v>150</v>
-      </c>
-      <c r="G45">
-        <v>150</v>
-      </c>
-      <c r="H45">
-        <v>25</v>
-      </c>
-      <c r="I45">
-        <v>150</v>
-      </c>
-      <c r="J45">
-        <v>150</v>
-      </c>
-      <c r="K45">
-        <v>-250</v>
-      </c>
-      <c r="L45">
-        <v>-50</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" t="s">
-        <v>78</v>
-      </c>
-      <c r="D46" t="s">
-        <v>96</v>
-      </c>
-      <c r="E46" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" t="s">
-        <v>21</v>
-      </c>
-      <c r="F48">
-        <v>100</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
       </c>
       <c r="H48">
         <v>25</v>
       </c>
-      <c r="I48" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I48">
+        <v>-150</v>
+      </c>
+      <c r="J48">
+        <v>-150</v>
+      </c>
+      <c r="K48">
+        <v>-250</v>
+      </c>
+      <c r="L48">
+        <v>-50</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="F49">
+        <v>150</v>
+      </c>
+      <c r="G49">
+        <v>-150</v>
+      </c>
+      <c r="H49">
+        <v>25</v>
+      </c>
+      <c r="I49">
+        <v>150</v>
+      </c>
+      <c r="J49">
+        <v>-150</v>
+      </c>
+      <c r="K49">
+        <v>-250</v>
+      </c>
+      <c r="L49">
+        <v>-50</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" t="s">
+        <v>110</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50">
+        <v>-150</v>
+      </c>
+      <c r="G50">
+        <v>150</v>
+      </c>
+      <c r="H50">
+        <v>25</v>
+      </c>
+      <c r="I50">
+        <v>-150</v>
+      </c>
+      <c r="J50">
+        <v>150</v>
+      </c>
+      <c r="K50">
+        <v>-250</v>
+      </c>
+      <c r="L50">
+        <v>-50</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="E51" t="s">
         <v>11</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H51">
-        <v>3037</v>
-      </c>
-      <c r="I51" t="s">
-        <v>82</v>
+        <v>25</v>
+      </c>
+      <c r="I51">
+        <v>150</v>
+      </c>
+      <c r="J51">
+        <v>150</v>
+      </c>
+      <c r="K51">
+        <v>-250</v>
+      </c>
+      <c r="L51">
+        <v>-50</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2148,269 +2265,175 @@
         <v>11</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
+        <v>94</v>
+      </c>
+    </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" t="s">
+        <v>21</v>
+      </c>
+      <c r="F54">
         <v>100</v>
       </c>
-      <c r="D54" t="s">
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>25</v>
+      </c>
+      <c r="I54" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" t="s">
+        <v>115</v>
+      </c>
+      <c r="D57" t="s">
+        <v>52</v>
+      </c>
+      <c r="E57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>3037</v>
+      </c>
+      <c r="I57" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C58" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58" t="s">
+        <v>52</v>
+      </c>
+      <c r="F58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C60" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" t="s">
         <v>23</v>
       </c>
-      <c r="E54" t="s">
-        <v>79</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
+      <c r="E60" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
         <v>3287</v>
       </c>
-      <c r="I54" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" t="s">
-        <v>100</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="I60" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C61" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" t="s">
         <v>25</v>
       </c>
-      <c r="E55" t="s">
-        <v>79</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
+      <c r="E61" t="s">
+        <v>94</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
         <v>3299</v>
       </c>
-      <c r="I55" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C56" t="s">
-        <v>100</v>
-      </c>
-      <c r="D56" t="s">
-        <v>96</v>
-      </c>
-      <c r="E56" t="s">
-        <v>23</v>
-      </c>
-      <c r="F56" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" t="s">
-        <v>69</v>
-      </c>
-      <c r="E58" t="s">
-        <v>70</v>
-      </c>
-      <c r="F58" t="s">
-        <v>83</v>
-      </c>
-      <c r="G58" t="s">
-        <v>84</v>
-      </c>
-      <c r="H58" t="s">
-        <v>85</v>
-      </c>
-      <c r="I58" t="s">
-        <v>86</v>
-      </c>
-      <c r="J58" t="s">
-        <v>87</v>
-      </c>
-      <c r="K58" t="s">
-        <v>88</v>
-      </c>
-      <c r="L58" t="s">
-        <v>89</v>
-      </c>
-      <c r="M58" t="s">
-        <v>90</v>
-      </c>
-      <c r="N58" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C59" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" t="s">
-        <v>103</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>-150</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>2400</v>
-      </c>
-      <c r="J59">
-        <v>-150</v>
-      </c>
-      <c r="K59">
-        <v>3000</v>
-      </c>
-      <c r="L59">
-        <v>170</v>
-      </c>
-      <c r="M59">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C60" t="s">
-        <v>102</v>
-      </c>
-      <c r="D60" t="s">
-        <v>104</v>
-      </c>
-      <c r="E60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60">
-        <v>2400</v>
-      </c>
-      <c r="G60">
-        <v>150</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>150</v>
-      </c>
-      <c r="K60">
-        <v>3000</v>
-      </c>
-      <c r="L60">
-        <v>170</v>
-      </c>
-      <c r="M60">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C61" t="s">
-        <v>102</v>
-      </c>
-      <c r="D61" t="s">
-        <v>57</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>1500</v>
-      </c>
-      <c r="I61">
-        <v>2400</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>1500</v>
-      </c>
-      <c r="L61">
-        <v>110</v>
-      </c>
-      <c r="M61">
-        <v>110</v>
-      </c>
-      <c r="N61">
-        <v>90</v>
+      <c r="I61" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2418,396 +2441,584 @@
         <v>11</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E62" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="F62" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C64" t="s">
         <v>2</v>
       </c>
       <c r="D64" t="s">
+        <v>84</v>
+      </c>
+      <c r="E64" t="s">
+        <v>85</v>
+      </c>
+      <c r="F64" t="s">
+        <v>99</v>
+      </c>
+      <c r="G64" t="s">
+        <v>100</v>
+      </c>
+      <c r="H64" t="s">
+        <v>101</v>
+      </c>
+      <c r="I64" t="s">
+        <v>102</v>
+      </c>
+      <c r="J64" t="s">
+        <v>103</v>
+      </c>
+      <c r="K64" t="s">
+        <v>104</v>
+      </c>
+      <c r="L64" t="s">
+        <v>105</v>
+      </c>
+      <c r="M64" t="s">
         <v>106</v>
       </c>
-      <c r="E64" t="s">
+      <c r="N64" t="s">
         <v>107</v>
       </c>
-      <c r="F64" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" t="s">
-        <v>8</v>
-      </c>
-      <c r="H64" t="s">
-        <v>9</v>
-      </c>
-      <c r="I64" t="s">
-        <v>10</v>
-      </c>
-      <c r="J64" t="s">
-        <v>108</v>
-      </c>
-      <c r="K64" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C65" t="s">
+        <v>118</v>
+      </c>
+      <c r="D65" t="s">
+        <v>119</v>
+      </c>
+      <c r="E65" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>-150</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>2400</v>
+      </c>
+      <c r="J65">
+        <v>-150</v>
+      </c>
+      <c r="K65">
+        <v>3000</v>
+      </c>
+      <c r="L65">
+        <v>170</v>
+      </c>
+      <c r="M65">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C66" t="s">
+        <v>118</v>
+      </c>
+      <c r="D66" t="s">
+        <v>120</v>
+      </c>
+      <c r="E66" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66">
+        <v>2400</v>
+      </c>
+      <c r="G66">
+        <v>150</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>150</v>
+      </c>
+      <c r="K66">
+        <v>3000</v>
+      </c>
+      <c r="L66">
+        <v>170</v>
+      </c>
+      <c r="M66">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C67" t="s">
+        <v>118</v>
+      </c>
+      <c r="D67" t="s">
+        <v>57</v>
+      </c>
+      <c r="E67" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>1500</v>
+      </c>
+      <c r="I67">
+        <v>2400</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>1500</v>
+      </c>
+      <c r="L67">
         <v>110</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C65" t="s">
-        <v>112</v>
-      </c>
-      <c r="D65" t="s">
-        <v>97</v>
-      </c>
-      <c r="E65" t="s">
-        <v>113</v>
-      </c>
-      <c r="F65">
-        <v>100</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C66" t="s">
-        <v>112</v>
-      </c>
-      <c r="D66" t="s">
-        <v>112</v>
-      </c>
-      <c r="E66" t="s">
-        <v>114</v>
-      </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>25</v>
-      </c>
-      <c r="I66" t="s">
-        <v>115</v>
-      </c>
-      <c r="J66">
+      <c r="M67">
+        <v>110</v>
+      </c>
+      <c r="N67">
         <v>90</v>
       </c>
-      <c r="K66">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C67" t="s">
-        <v>112</v>
-      </c>
-      <c r="D67" t="s">
-        <v>112</v>
-      </c>
-      <c r="E67" t="s">
-        <v>116</v>
-      </c>
-      <c r="F67">
-        <v>2400</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D68" t="s">
         <v>112</v>
       </c>
       <c r="E68" t="s">
+        <v>119</v>
+      </c>
+      <c r="F68" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" t="s">
+        <v>122</v>
+      </c>
+      <c r="E70" t="s">
+        <v>123</v>
+      </c>
+      <c r="F70" t="s">
+        <v>7</v>
+      </c>
+      <c r="G70" t="s">
+        <v>8</v>
+      </c>
+      <c r="H70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I70" t="s">
+        <v>10</v>
+      </c>
+      <c r="J70" t="s">
+        <v>124</v>
+      </c>
+      <c r="K70" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C71" t="s">
+        <v>128</v>
+      </c>
+      <c r="D71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E71" t="s">
+        <v>129</v>
+      </c>
+      <c r="F71">
+        <v>100</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C72" t="s">
+        <v>128</v>
+      </c>
+      <c r="D72" t="s">
+        <v>128</v>
+      </c>
+      <c r="E72" t="s">
+        <v>130</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>25</v>
+      </c>
+      <c r="I72" t="s">
+        <v>131</v>
+      </c>
+      <c r="J72">
+        <v>90</v>
+      </c>
+      <c r="K72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C73" t="s">
+        <v>128</v>
+      </c>
+      <c r="D73" t="s">
+        <v>128</v>
+      </c>
+      <c r="E73" t="s">
+        <v>132</v>
+      </c>
+      <c r="F73">
+        <v>2400</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C74" t="s">
+        <v>128</v>
+      </c>
+      <c r="D74" t="s">
+        <v>128</v>
+      </c>
+      <c r="E74" t="s">
+        <v>132</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>3000</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C76" t="s">
+        <v>134</v>
+      </c>
+      <c r="D76" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" t="s">
+        <v>129</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" t="s">
+        <v>134</v>
+      </c>
+      <c r="D77" t="s">
+        <v>93</v>
+      </c>
+      <c r="E77" t="s">
+        <v>135</v>
+      </c>
+      <c r="F77">
+        <v>1200</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C78" t="s">
+        <v>134</v>
+      </c>
+      <c r="D78" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78" t="s">
+        <v>129</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C79" t="s">
+        <v>134</v>
+      </c>
+      <c r="D79" t="s">
+        <v>118</v>
+      </c>
+      <c r="E79" t="s">
+        <v>129</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>-150</v>
+      </c>
+      <c r="H79">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C80" t="s">
+        <v>134</v>
+      </c>
+      <c r="D80" t="s">
         <v>116</v>
       </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68">
+      <c r="E80" t="s">
+        <v>129</v>
+      </c>
+      <c r="F80">
+        <v>1200</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C81" t="s">
+        <v>134</v>
+      </c>
+      <c r="D81" t="s">
+        <v>134</v>
+      </c>
+      <c r="E81" t="s">
+        <v>132</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
         <v>3000</v>
       </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C70" t="s">
-        <v>118</v>
-      </c>
-      <c r="D70" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" t="s">
-        <v>113</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C71" t="s">
-        <v>118</v>
-      </c>
-      <c r="D71" t="s">
-        <v>78</v>
-      </c>
-      <c r="E71" t="s">
-        <v>119</v>
-      </c>
-      <c r="F71">
-        <v>1200</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C72" t="s">
-        <v>118</v>
-      </c>
-      <c r="D72" t="s">
-        <v>99</v>
-      </c>
-      <c r="E72" t="s">
-        <v>113</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>3037</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C73" t="s">
-        <v>118</v>
-      </c>
-      <c r="D73" t="s">
-        <v>102</v>
-      </c>
-      <c r="E73" t="s">
-        <v>113</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73">
-        <v>-150</v>
-      </c>
-      <c r="H73">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C74" t="s">
-        <v>118</v>
-      </c>
-      <c r="D74" t="s">
-        <v>100</v>
-      </c>
-      <c r="E74" t="s">
-        <v>113</v>
-      </c>
-      <c r="F74">
-        <v>1200</v>
-      </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C75" t="s">
-        <v>118</v>
-      </c>
-      <c r="D75" t="s">
-        <v>118</v>
-      </c>
-      <c r="E75" t="s">
-        <v>116</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="G75">
-        <v>3000</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>121</v>
-      </c>
-      <c r="C76" t="s">
-        <v>112</v>
-      </c>
-      <c r="D76" t="s">
-        <v>122</v>
-      </c>
-      <c r="G76">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>137</v>
+      </c>
+      <c r="C82" t="s">
+        <v>128</v>
+      </c>
+      <c r="D82" t="s">
+        <v>138</v>
+      </c>
+      <c r="G82">
         <v>50</v>
       </c>
-      <c r="H76" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>124</v>
-      </c>
-      <c r="C77" t="s">
-        <v>125</v>
-      </c>
-      <c r="D77" t="s">
-        <v>126</v>
-      </c>
-      <c r="E77">
+      <c r="H82" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>140</v>
+      </c>
+      <c r="C83" t="s">
+        <v>141</v>
+      </c>
+      <c r="D83" t="s">
+        <v>142</v>
+      </c>
+      <c r="E83">
         <v>10</v>
       </c>
-      <c r="F77" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>124</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="F83" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>140</v>
+      </c>
+      <c r="C84" t="s">
         <v>48</v>
       </c>
-      <c r="D78" t="s">
-        <v>126</v>
-      </c>
-      <c r="E78">
+      <c r="D84" t="s">
+        <v>142</v>
+      </c>
+      <c r="E84">
         <v>20</v>
       </c>
-      <c r="F78" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>129</v>
+      <c r="F84" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
